--- a/src/examples/ELV/data/ELV_ICE_processes.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_processes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -49,6 +49,24 @@
     <t xml:space="preserve">cost_operation</t>
   </si>
   <si>
+    <t xml:space="preserve">collection_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_cl_ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection of an ice car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market</t>
+  </si>
+  <si>
     <t xml:space="preserve">dismantling_ICE</t>
   </si>
   <si>
@@ -61,9 +79,6 @@
     <t xml:space="preserve">manual, mechanical</t>
   </si>
   <si>
-    <t xml:space="preserve">ELV</t>
-  </si>
-  <si>
     <t xml:space="preserve">component</t>
   </si>
   <si>
@@ -154,28 +169,100 @@
     <t xml:space="preserve">smelting of ferrous fractions</t>
   </si>
   <si>
-    <t xml:space="preserve">market_wasterubber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">market</t>
+    <t xml:space="preserve">market_waste_rubber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mkt_w_rub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste rubber</t>
   </si>
   <si>
     <t xml:space="preserve">market_ree</t>
   </si>
   <si>
+    <t xml:space="preserve">mkt_w_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste REE mix</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_lead</t>
   </si>
   <si>
+    <t xml:space="preserve">mkt_w_pb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste lead</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_H2SO4</t>
   </si>
   <si>
+    <t xml:space="preserve">mkt_w_H2SO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste H2SO4</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_nonferrous</t>
   </si>
   <si>
+    <t xml:space="preserve">mkt_w_nfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste non-ferrous</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_ferrous</t>
   </si>
   <si>
+    <t xml:space="preserve">mkt_w_fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste ferrous</t>
+  </si>
+  <si>
     <t xml:space="preserve">market_waste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mkt_w_gen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste (general)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mkt_w_gls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mkt_w_pla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_slag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mkt_w_slag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste slag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_waste_oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market for waste oil</t>
   </si>
 </sst>
 </file>
@@ -190,6 +277,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -255,12 +343,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -285,166 +377,166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="21.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="0" t="n">
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <f aca="false">G2*H2/10</f>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <f aca="false">G3*H3/10</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="0" t="n">
-        <f aca="false">G3*H3/10</f>
+      <c r="I4" s="1" t="n">
+        <f aca="false">G4*H4/10</f>
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="0" t="s">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="0" t="n">
-        <f aca="false">G4*H4/10</f>
+      <c r="I5" s="1" t="n">
+        <f aca="false">G5*H5/10</f>
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <f aca="false">G5*H5/100</f>
-        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -458,241 +550,393 @@
         <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <f aca="false">G6*H6/100</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I6" s="0" t="n">
-        <f aca="false">G6*H6/10</f>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <f aca="false">G7*H7/10</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="B8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="F8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <f aca="false">G8*H8/10</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="I8" s="0" t="n">
-        <f aca="false">G8*H8/10</f>
+      <c r="I9" s="1" t="n">
+        <f aca="false">G9*H9/10</f>
         <v>25.2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="0" t="s">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="I9" s="0" t="n">
-        <f aca="false">G9*H9/100</f>
+      <c r="I10" s="1" t="n">
+        <f aca="false">G10*H10/100</f>
         <v>18.9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="0" t="s">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="0" t="n">
+      <c r="F11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H11" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="I10" s="0" t="n">
-        <f aca="false">G10*H10/100</f>
+      <c r="I11" s="1" t="n">
+        <f aca="false">G11*H11/100</f>
         <v>19.8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="0" t="n">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>-5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="0" t="n">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>-2000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="0" t="n">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>-20</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="0" t="n">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>-10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="0" t="n">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>-5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="0" t="n">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>-4</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="0" t="n">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/examples/ELV/data/ELV_ICE_processes.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_processes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="84">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t xml:space="preserve">component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market_reuse_ELVcomponents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ru_com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">direct or indirect reuse of components from an elv</t>
   </si>
   <si>
     <t xml:space="preserve">shredding_engtrans</t>
@@ -377,7 +386,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.53"/>
@@ -480,7 +489,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -489,140 +498,130 @@
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <f aca="false">G4*H4/10</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
         <f aca="false">G5*H5/10</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <f aca="false">G6*H6/10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="C7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <f aca="false">G6*H6/100</f>
+      <c r="I7" s="1" t="n">
+        <f aca="false">G7*H7/100</f>
         <v>10</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="1" t="n">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <f aca="false">G7*H7/10</f>
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="I8" s="1" t="n">
         <f aca="false">G8*H8/10</f>
@@ -640,23 +639,23 @@
         <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="I9" s="1" t="n">
         <f aca="false">G9*H9/10</f>
-        <v>25.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -669,24 +668,24 @@
       <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>32</v>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>33</v>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>42</v>
       </c>
       <c r="I10" s="1" t="n">
-        <f aca="false">G10*H10/100</f>
-        <v>18.9</v>
+        <f aca="false">G10*H10/10</f>
+        <v>25.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -700,27 +699,27 @@
         <v>48</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I11" s="1" t="n">
         <f aca="false">G11*H11/100</f>
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -730,13 +729,23 @@
         <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>33</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>-5</v>
+        <f aca="false">G12*H12/100</f>
+        <v>19.8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -756,7 +765,7 @@
         <v>14</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>-2000</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -776,7 +785,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="1" t="n">
-        <v>-20</v>
+        <v>-2000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -796,7 +805,7 @@
         <v>14</v>
       </c>
       <c r="I15" s="1" t="n">
-        <v>-10</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -816,7 +825,7 @@
         <v>14</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -836,7 +845,7 @@
         <v>14</v>
       </c>
       <c r="I17" s="1" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -856,7 +865,7 @@
         <v>14</v>
       </c>
       <c r="I18" s="1" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -876,7 +885,7 @@
         <v>14</v>
       </c>
       <c r="I19" s="1" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -896,7 +905,7 @@
         <v>14</v>
       </c>
       <c r="I20" s="1" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -916,7 +925,7 @@
         <v>14</v>
       </c>
       <c r="I21" s="1" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -924,10 +933,10 @@
         <v>79</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>14</v>
@@ -936,6 +945,26 @@
         <v>14</v>
       </c>
       <c r="I22" s="1" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>3</v>
       </c>
     </row>

--- a/src/examples/ELV/data/ELV_ICE_processes.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_processes.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="88">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -272,6 +272,18 @@
   </si>
   <si>
     <t xml:space="preserve">market for waste oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PutOnMarket_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_pom_ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">put on market for ICE vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input</t>
   </si>
 </sst>
 </file>
@@ -386,7 +398,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.53"/>
@@ -968,6 +980,23 @@
         <v>3</v>
       </c>
     </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/src/examples/ELV/data/ELV_ICE_processes.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_processes.xlsx
@@ -990,7 +990,7 @@
       <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
